--- a/salesforce_forms/039_warranty_enquiry_form--salesforce_forms.xlsx
+++ b/salesforce_forms/039_warranty_enquiry_form--salesforce_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>product_serial_number</t>
+          <t>What is the product serial number?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>customer_name</t>
+          <t>What is your name?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>customer_phone</t>
+          <t>What is your phone number?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,13 +594,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>customer_email</t>
+          <t>What is your email address?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>product_description</t>
+          <t>What is the description of the issue?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,92 +630,92 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>claim_date</t>
+          <t>warranty_type</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>claim_date</t>
+          <t>What is the warranty type?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>issue_description</t>
+          <t>claim_status</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>issue_description</t>
+          <t>What is the claim status?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>customer_address</t>
+          <t>claim_date</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>customer_address</t>
+          <t>What is the claim date?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>claim_type</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>What is the claim type?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>customer_postal_code</t>
+          <t>contact_name</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>customer_postal_code</t>
+          <t>What is the contact name?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>warranty_type</t>
+          <t>warranty_start_date</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>warranty_type</t>
+          <t>What is the warranty start date?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,430 +773,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>warranty_start_date</t>
+          <t>warranty_end_date</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>warranty_start_date</t>
+          <t>What is the warranty end date?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>warranty_end_date</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>warranty_end_date</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>claim_status</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>claim_status</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>claim_date</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>claim_date</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>claim_type</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>claim_type</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>contact_name</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>contact_name</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>claim_status</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>claim_status</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>claim_date</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>claim_date</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>issue_description</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>issue_description</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>claim_status</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>claim_status</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>warranty_start_date</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>warranty_start_date</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>warranty_end_date</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>warranty_end_date</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>claim_type</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>claim_type</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>customer_phone</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>customer_phone</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>product_serial_number</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>product_serial_number</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>issue_description</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>issue_description</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>warranty_type</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>warranty_type</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>claim_status</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>claim_status</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>claim_date</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>claim_date</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1217,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1246,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'standard'}</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Standard'}</t>
+          <t>Standard</t>
         </is>
       </c>
     </row>
@@ -1263,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'extended'}</t>
+          <t>extended</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Extended'}</t>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -1280,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'not_started'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Not Started'}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -1297,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1314,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1331,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'mechanical'}</t>
+          <t>mechanical</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Mechanical'}</t>
+          <t>Mechanical</t>
         </is>
       </c>
     </row>
@@ -1348,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'electrical'}</t>
+          <t>electrical</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Electrical'}</t>
+          <t>Electrical</t>
         </is>
       </c>
     </row>
@@ -1365,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
